--- a/maintenance_forms/023_dry_type_transformer_maintenance_checklist--maintenance_forms.xlsx
+++ b/maintenance_forms/023_dry_type_transformer_maintenance_checklist--maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Passed'}</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Passed'}</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'dry_coupling'}</t>
+          <t>dry_coupling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Dry coupling'}</t>
+          <t>Dry coupling</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'dry_coupling_-_ground_fault'}</t>
+          <t>dry_coupling_-_ground_fault</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Dry coupling - Ground fault'}</t>
+          <t>Dry coupling - Ground fault</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'dry_coupling_-_ground_fault_-_insulated'}</t>
+          <t>dry_coupling_-_ground_fault_-_insulated</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Dry coupling - Ground fault - Insulated'}</t>
+          <t>Dry coupling - Ground fault - Insulated</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'dry_coupling_-_ground_fault_-_insulated_-_1_kv'}</t>
+          <t>dry_coupling_-_ground_fault_-_insulated_-_1_kv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Dry coupling - Ground fault - Insulated - 1 kV'}</t>
+          <t>Dry coupling - Ground fault - Insulated - 1 kV</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'dry_coupling_-_ground_fault_-_insulated_-_1_kv_-_2'}</t>
+          <t>dry_coupling_-_ground_fault_-_insulated_-_1_kv_-_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Dry coupling - Ground fault - Insulated - 1 kV - 2'}</t>
+          <t>Dry coupling - Ground fault - Insulated - 1 kV - 2</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'dry_coupling_-_ground_fault_-_insulated_-_1_kv_-_2_-_2'}</t>
+          <t>dry_coupling_-_ground_fault_-_insulated_-_1_kv_-_2_-_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Dry coupling - Ground fault - Insulated - 1 kV - 2 - 2'}</t>
+          <t>Dry coupling - Ground fault - Insulated - 1 kV - 2 - 2</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'semi-annually'}</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Semi-Annually'}</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'not_terminated'}</t>
+          <t>not_terminated</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Not terminated'}</t>
+          <t>Not terminated</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
